--- a/aulas/09set/A55_UC01_11set/public/dados/dengue_pr_comparado.xlsx
+++ b/aulas/09set/A55_UC01_11set/public/dados/dengue_pr_comparado.xlsx
@@ -5640,7 +5640,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5700,7 +5700,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5730,7 +5730,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5760,7 +5760,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5790,7 +5790,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5820,7 +5820,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5850,7 +5850,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5880,7 +5880,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5910,7 +5910,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5940,7 +5940,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5970,7 +5970,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6000,7 +6000,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6060,7 +6060,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6090,7 +6090,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6120,7 +6120,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6150,7 +6150,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6180,7 +6180,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6240,7 +6240,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6270,7 +6270,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6300,7 +6300,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6330,7 +6330,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -13665,7 +13665,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
